--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-11139_fixTypeNotFoundError.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-11139_fixTypeNotFoundError.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve"> 11:00 AM</t>
   </si>
   <si>
-    <t>20:00 PM</t>
+    <t>8:00 PM</t>
   </si>
   <si>
     <t>2019-01-10T10:15:00Z[UTC]</t>
